--- a/ProTest/src/main/java/com/utility/Calculation.xlsx
+++ b/ProTest/src/main/java/com/utility/Calculation.xlsx
@@ -11,30 +11,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>FlooreThickness</t>
-  </si>
-  <si>
-    <t>AtticLength</t>
-  </si>
-  <si>
-    <t>AtticWidth</t>
-  </si>
-  <si>
-    <t>InternalRidgeHeight</t>
-  </si>
-  <si>
-    <t>HalfSpan</t>
-  </si>
-  <si>
-    <t>SurfaceToInsulate</t>
-  </si>
-  <si>
-    <t>TotalSurface</t>
-  </si>
-  <si>
-    <t>ReccomenedThickness</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>atticWidthL</t>
+  </si>
+  <si>
+    <t>atticWidthL1</t>
+  </si>
+  <si>
+    <t>atticWidthL2</t>
+  </si>
+  <si>
+    <t>atticWidthL3</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>h1</t>
+  </si>
+  <si>
+    <t>h2</t>
+  </si>
+  <si>
+    <t>floorThickness</t>
+  </si>
+  <si>
+    <t>totalSurface</t>
+  </si>
+  <si>
+    <t>totalSurface1</t>
+  </si>
+  <si>
+    <t>totalSurface2</t>
+  </si>
+  <si>
+    <t>surfaceToInsulate</t>
+  </si>
+  <si>
+    <t>insulationThicknessToInstall</t>
   </si>
 </sst>
 </file>
@@ -296,6 +311,8 @@
     <col customWidth="1" min="4" max="4" width="15.88"/>
     <col customWidth="1" min="6" max="6" width="15.25"/>
     <col customWidth="1" min="8" max="8" width="18.88"/>
+    <col customWidth="1" min="12" max="12" width="14.5"/>
+    <col customWidth="1" min="13" max="13" width="21.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -323,31 +340,61 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G2" s="1">
         <v>11.0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="H2" s="1">
         <v>8.9</v>
       </c>
-      <c r="C2" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="D2" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="I2" s="1">
         <v>5.0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="J2" s="1">
         <v>89.3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="K2" s="1">
         <v>100.0</v>
       </c>
-      <c r="H2" s="1">
-        <v>220.0</v>
+      <c r="L2" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>100.0</v>
       </c>
     </row>
     <row r="3">
@@ -375,6 +422,21 @@
       <c r="H3" s="1">
         <v>220.0</v>
       </c>
+      <c r="I3" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>100.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
@@ -400,6 +462,21 @@
       </c>
       <c r="H4" s="1">
         <v>220.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>110.0</v>
       </c>
     </row>
   </sheetData>

--- a/ProTest/src/main/java/com/utility/Calculation.xlsx
+++ b/ProTest/src/main/java/com/utility/Calculation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>atticWidthL</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>insulationThicknessToInstall</t>
+  </si>
+  <si>
+    <t>finalResult</t>
   </si>
 </sst>
 </file>
@@ -355,6 +358,9 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -379,7 +385,7 @@
         <v>11.0</v>
       </c>
       <c r="H2" s="1">
-        <v>8.9</v>
+        <v>158.0</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -395,6 +401,9 @@
       </c>
       <c r="M2" s="1">
         <v>100.0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>15007.0</v>
       </c>
     </row>
     <row r="3">
@@ -437,6 +446,9 @@
       <c r="M3" s="1">
         <v>100.0</v>
       </c>
+      <c r="N3" s="1">
+        <v>12217.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
@@ -477,6 +489,9 @@
       </c>
       <c r="M4" s="1">
         <v>110.0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>5195.0</v>
       </c>
     </row>
   </sheetData>
